--- a/research/traditional_assets/database/data/belgium/belgium_advertising.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_advertising.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.01955172413793103</v>
+        <v>-0.1199324324324324</v>
       </c>
       <c r="H2">
-        <v>0.01955172413793103</v>
+        <v>-0.2074324324324324</v>
       </c>
       <c r="I2">
-        <v>-0.04344827586206897</v>
+        <v>-0.179054054054054</v>
       </c>
       <c r="J2">
-        <v>-0.04344827586206897</v>
+        <v>-0.179054054054054</v>
       </c>
       <c r="K2">
-        <v>-1.17</v>
+        <v>-7.25</v>
       </c>
       <c r="L2">
-        <v>-0.0403448275862069</v>
+        <v>-0.2449324324324324</v>
       </c>
       <c r="M2">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="N2">
-        <v>0.003254437869822486</v>
+        <v>0.02679245283018868</v>
       </c>
       <c r="O2">
-        <v>-0.09401709401709403</v>
+        <v>-0.09793103448275861</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>22</v>
+        <v>18.9</v>
       </c>
       <c r="V2">
-        <v>0.6508875739644971</v>
+        <v>0.7132075471698113</v>
       </c>
       <c r="W2">
-        <v>-0.078</v>
+        <v>-0.2735849056603774</v>
       </c>
       <c r="X2">
-        <v>0.1314711854686828</v>
+        <v>0.1210490217870816</v>
       </c>
       <c r="Y2">
-        <v>-0.2094711854686828</v>
+        <v>-0.394633927447459</v>
       </c>
       <c r="Z2">
-        <v>3.419811320754717</v>
+        <v>3.605359317904995</v>
       </c>
       <c r="AA2">
-        <v>-0.1485849056603774</v>
+        <v>-0.6455542021924484</v>
       </c>
       <c r="AB2">
-        <v>0.118862309153339</v>
+        <v>0.1025115326986335</v>
       </c>
       <c r="AC2">
-        <v>-0.2674472148137164</v>
+        <v>-0.748065734891082</v>
       </c>
       <c r="AD2">
-        <v>5.91</v>
+        <v>8.26</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.91</v>
+        <v>8.26</v>
       </c>
       <c r="AG2">
-        <v>-16.09</v>
+        <v>-10.64</v>
       </c>
       <c r="AH2">
-        <v>0.1488290103248552</v>
+        <v>0.2376294591484465</v>
       </c>
       <c r="AI2">
-        <v>0.1823511261956187</v>
+        <v>0.2676604018146468</v>
       </c>
       <c r="AJ2">
-        <v>-0.9085262563523434</v>
+        <v>-0.6708701134930641</v>
       </c>
       <c r="AK2">
-        <v>-1.545629202689721</v>
+        <v>-0.8896321070234111</v>
       </c>
       <c r="AL2">
-        <v>0.258</v>
+        <v>0.441</v>
       </c>
       <c r="AM2">
-        <v>0.258</v>
+        <v>0.441</v>
       </c>
       <c r="AN2">
-        <v>-3.94</v>
+        <v>-1.61328125</v>
       </c>
       <c r="AO2">
-        <v>-4.883720930232558</v>
+        <v>-12.01814058956916</v>
       </c>
       <c r="AP2">
-        <v>10.72666666666667</v>
+        <v>2.078125</v>
       </c>
       <c r="AQ2">
-        <v>-4.883720930232558</v>
+        <v>-12.01814058956916</v>
       </c>
     </row>
     <row r="3">
@@ -716,31 +716,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.01955172413793103</v>
+        <v>-0.1199324324324324</v>
       </c>
       <c r="H3">
-        <v>0.01955172413793103</v>
+        <v>-0.2074324324324324</v>
       </c>
       <c r="I3">
-        <v>-0.04344827586206897</v>
+        <v>-0.179054054054054</v>
       </c>
       <c r="J3">
-        <v>-0.04344827586206897</v>
+        <v>-0.179054054054054</v>
       </c>
       <c r="K3">
-        <v>-1.17</v>
+        <v>-7.25</v>
       </c>
       <c r="L3">
-        <v>-0.0403448275862069</v>
+        <v>-0.2449324324324324</v>
       </c>
       <c r="M3">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="N3">
-        <v>0.003254437869822486</v>
+        <v>0.02679245283018868</v>
       </c>
       <c r="O3">
-        <v>-0.09401709401709403</v>
+        <v>-0.09793103448275861</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>22</v>
+        <v>18.9</v>
       </c>
       <c r="V3">
-        <v>0.6508875739644971</v>
+        <v>0.7132075471698113</v>
       </c>
       <c r="W3">
-        <v>-0.078</v>
+        <v>-0.2735849056603774</v>
       </c>
       <c r="X3">
-        <v>0.1314711854686828</v>
+        <v>0.1210490217870816</v>
       </c>
       <c r="Y3">
-        <v>-0.2094711854686828</v>
+        <v>-0.394633927447459</v>
       </c>
       <c r="Z3">
-        <v>3.419811320754717</v>
+        <v>3.605359317904995</v>
       </c>
       <c r="AA3">
-        <v>-0.1485849056603774</v>
+        <v>-0.6455542021924484</v>
       </c>
       <c r="AB3">
-        <v>0.118862309153339</v>
+        <v>0.1025115326986335</v>
       </c>
       <c r="AC3">
-        <v>-0.2674472148137164</v>
+        <v>-0.748065734891082</v>
       </c>
       <c r="AD3">
-        <v>5.91</v>
+        <v>8.26</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.91</v>
+        <v>8.26</v>
       </c>
       <c r="AG3">
-        <v>-16.09</v>
+        <v>-10.64</v>
       </c>
       <c r="AH3">
-        <v>0.1488290103248552</v>
+        <v>0.2376294591484465</v>
       </c>
       <c r="AI3">
-        <v>0.1823511261956187</v>
+        <v>0.2676604018146468</v>
       </c>
       <c r="AJ3">
-        <v>-0.9085262563523434</v>
+        <v>-0.6708701134930641</v>
       </c>
       <c r="AK3">
-        <v>-1.545629202689721</v>
+        <v>-0.8896321070234111</v>
       </c>
       <c r="AL3">
-        <v>0.258</v>
+        <v>0.441</v>
       </c>
       <c r="AM3">
-        <v>0.258</v>
+        <v>0.441</v>
       </c>
       <c r="AN3">
-        <v>-3.94</v>
+        <v>-1.61328125</v>
       </c>
       <c r="AO3">
-        <v>-4.883720930232558</v>
+        <v>-12.01814058956916</v>
       </c>
       <c r="AP3">
-        <v>10.72666666666667</v>
+        <v>2.078125</v>
       </c>
       <c r="AQ3">
-        <v>-4.883720930232558</v>
+        <v>-12.01814058956916</v>
       </c>
     </row>
   </sheetData>
